--- a/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
@@ -1,128 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\05 - WorkedHourPointing\01 - LP's\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD42718-502D-4E53-9706-3B477DE35876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>LPs</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>LP052409</t>
-  </si>
-  <si>
-    <t>LP052678</t>
-  </si>
-  <si>
-    <t>LP052681</t>
-  </si>
-  <si>
-    <t>LP052680</t>
-  </si>
-  <si>
-    <t>LP052609</t>
-  </si>
-  <si>
-    <t>LP052677</t>
-  </si>
-  <si>
-    <t>LP052749</t>
-  </si>
-  <si>
-    <t>LP052750</t>
-  </si>
-  <si>
-    <t>LP052774</t>
-  </si>
-  <si>
-    <t>LP052773</t>
-  </si>
-  <si>
-    <t>LP053211</t>
-  </si>
-  <si>
-    <t>LP052912</t>
-  </si>
-  <si>
-    <t>LP053100</t>
-  </si>
-  <si>
-    <t>LP053107</t>
-  </si>
-  <si>
-    <t>LP052983</t>
-  </si>
-  <si>
-    <t>LP052984</t>
-  </si>
-  <si>
-    <t>LP052734</t>
-  </si>
-  <si>
-    <t>LP053217</t>
-  </si>
-  <si>
-    <t>LP053216</t>
-  </si>
-  <si>
-    <t>LP053215</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -137,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -461,120 +420,216 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>21</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LPs</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LP053953</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Line created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LP053951</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Line created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LP053950</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Line created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LP053949</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Line created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LP053948</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Line created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LP053940</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Line created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LP053804</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Line created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LP053799</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Line created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LP053828</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Line created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LP053893</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Line created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LP053827</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Line created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LP053883</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Line created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LP054158</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LP doesn't exist!</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LP054161</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LP doesn't exist!</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LP054160</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LP doesn't exist!</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LP054159</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LP doesn't exist!</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,194 +443,402 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LP053953</t>
+          <t>LP053407</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Line created!</t>
+          <t>Apointing created!</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LP053951</t>
+          <t>LP053410</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Line created!</t>
+          <t>Apointing created!</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LP053950</t>
+          <t>LP053412</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Line created!</t>
+          <t>Apointing created!</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LP053949</t>
+          <t>LP053411</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Line created!</t>
+          <t>Apointing created!</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LP053948</t>
+          <t>LP053414</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Line created!</t>
+          <t>Apointing created!</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LP053940</t>
+          <t>LP053415</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Line created!</t>
+          <t>Apointing created!</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LP053804</t>
+          <t>LP053418</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Line created!</t>
+          <t>Apointing created!</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LP053799</t>
+          <t>LP053419</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Line created!</t>
+          <t>Apointing created!</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LP053828</t>
+          <t>LP052787</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Line created!</t>
+          <t>Apointing created!</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LP053893</t>
+          <t>LP053085</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Line created!</t>
+          <t>Apointing created!</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LP053827</t>
+          <t>LP053086</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Line created!</t>
+          <t>Apointing created!</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LP053883</t>
+          <t>LP053084</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Line created!</t>
+          <t>Apointing created!</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LP054158</t>
+          <t>LP053083</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LP doesn't exist!</t>
+          <t>Apointing created!</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LP054161</t>
+          <t>LP053082</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LP doesn't exist!</t>
+          <t>Apointing created!</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LP054160</t>
+          <t>LP053081</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LP doesn't exist!</t>
+          <t>Apointing created!</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LP054159</t>
+          <t>LP053080</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LP doesn't exist!</t>
-        </is>
-      </c>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LP052899</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LP053055</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LP053053</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LP053054</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LP053037</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LP053036</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LP053035</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LP053034</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LP053033</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LP053032</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LP053029</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LP052977</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LP052978</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LP053426</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LP053427</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LP053428</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LP052990</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LP052989</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LP052991</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LP052992</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
@@ -1,37 +1,153 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\04 - Pointing\01 - LP's\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930E7182-D919-4259-8989-9D7CAA17BA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
+  <si>
+    <t>LPs</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>LP053432</t>
+  </si>
+  <si>
+    <t>Apointing created!</t>
+  </si>
+  <si>
+    <t>LP053023</t>
+  </si>
+  <si>
+    <t>LP053218</t>
+  </si>
+  <si>
+    <t>LP053436</t>
+  </si>
+  <si>
+    <t>LP053265</t>
+  </si>
+  <si>
+    <t>LP053258</t>
+  </si>
+  <si>
+    <t>LP053232</t>
+  </si>
+  <si>
+    <t>LP053231</t>
+  </si>
+  <si>
+    <t>LP053257</t>
+  </si>
+  <si>
+    <t>LP053256</t>
+  </si>
+  <si>
+    <t>LP053255</t>
+  </si>
+  <si>
+    <t>LP053254</t>
+  </si>
+  <si>
+    <t>LP053253</t>
+  </si>
+  <si>
+    <t>LP053438</t>
+  </si>
+  <si>
+    <t>LP053442</t>
+  </si>
+  <si>
+    <t>LP053440</t>
+  </si>
+  <si>
+    <t>LP053210</t>
+  </si>
+  <si>
+    <t>LP053249</t>
+  </si>
+  <si>
+    <t>LP053248</t>
+  </si>
+  <si>
+    <t>LP053444</t>
+  </si>
+  <si>
+    <t>LP053445</t>
+  </si>
+  <si>
+    <t>LP053304</t>
+  </si>
+  <si>
+    <t>LP053563</t>
+  </si>
+  <si>
+    <t>LP053568</t>
+  </si>
+  <si>
+    <t>LP053565</t>
+  </si>
+  <si>
+    <t>LP054834</t>
+  </si>
+  <si>
+    <t>LP054835</t>
+  </si>
+  <si>
+    <t>LP054836</t>
+  </si>
+  <si>
+    <t>LP054188</t>
+  </si>
+  <si>
+    <t>LP054187</t>
+  </si>
+  <si>
+    <t>LP054186</t>
+  </si>
+  <si>
+    <t>LP054185</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +162,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,216 +486,276 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>LPs</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>LP053953</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Line created!</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>LP053951</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Line created!</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>LP053950</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Line created!</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LP053949</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Line created!</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LP053948</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Line created!</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LP053940</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Line created!</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LP053804</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Line created!</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>LP053799</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Line created!</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LP053828</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Line created!</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>LP053893</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Line created!</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>LP053827</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Line created!</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>LP053883</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Line created!</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>LP054158</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>LP doesn't exist!</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>LP054161</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>LP doesn't exist!</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>LP054160</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>LP doesn't exist!</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LP054159</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>LP doesn't exist!</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,7 +443,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LP053407</t>
+          <t>LP056045</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -455,7 +455,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LP053410</t>
+          <t>LP056046</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -467,7 +467,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LP053412</t>
+          <t>LP055670</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LP053411</t>
+          <t>LP055814</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LP053414</t>
+          <t>LP055840</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LP053415</t>
+          <t>LP055702</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LP053418</t>
+          <t>LP055703</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LP053419</t>
+          <t>LP055839</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LP052787</t>
+          <t>LP055838</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LP053085</t>
+          <t>LP055837</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LP053086</t>
+          <t>LP055950</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LP053084</t>
+          <t>LP055951</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LP053083</t>
+          <t>LP055952</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LP053082</t>
+          <t>LP055768</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -611,7 +611,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LP053081</t>
+          <t>LP055767</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LP053080</t>
+          <t>LP055439</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LP052899</t>
+          <t>LP055336</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LP053055</t>
+          <t>LP054978</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LP053053</t>
+          <t>LP054616</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LP053054</t>
+          <t>LP054604</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LP053037</t>
+          <t>LP054603</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -695,7 +695,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LP053036</t>
+          <t>LP055891</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -707,7 +707,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LP053035</t>
+          <t>LP055893</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LP053034</t>
+          <t>LP055890</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LP053033</t>
+          <t>LP055492</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LP053032</t>
+          <t>LP055738</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LP053029</t>
+          <t>LP055737</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -767,7 +767,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LP052977</t>
+          <t>LP055736</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -779,66 +779,38 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LP052978</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>LP055442</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LP053426</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>LP055735</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LP053427</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>LP053428</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>LP052990</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>LP052989</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>LP052991</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>LP052992</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>LP055686</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,7 +443,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LP056045</t>
+          <t>LP055065</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -455,7 +455,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LP056046</t>
+          <t>LP055066</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -467,7 +467,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LP055670</t>
+          <t>LP055067</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LP055814</t>
+          <t>LP055723</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LP055840</t>
+          <t>LP055900</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LP055702</t>
+          <t>LP056278</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LP055703</t>
+          <t>LP055074</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LP055839</t>
+          <t>LP055197</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LP055838</t>
+          <t>LP055370</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LP055837</t>
+          <t>LP055390</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -563,31 +563,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LP055950</t>
+          <t>LP055442</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Apointing created!</t>
+          <t>LP already have pointing!</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LP055951</t>
+          <t>LP055735</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Apointing created!</t>
+          <t>LP already have pointing!</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LP055952</t>
+          <t>LP056041</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LP055768</t>
+          <t>LP056042</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -611,7 +611,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LP055767</t>
+          <t>LP056043</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LP055439</t>
+          <t>LP056044</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LP055336</t>
+          <t>LP056534</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LP054978</t>
+          <t>LP056535</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LP054616</t>
+          <t>LP056536</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LP054604</t>
+          <t>LP056537</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LP054603</t>
+          <t>LP056005</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -695,7 +695,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LP055891</t>
+          <t>LP056006</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -707,7 +707,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LP055893</t>
+          <t>LP056007</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LP055890</t>
+          <t>LP056047</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LP055492</t>
+          <t>LP055701</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LP055738</t>
+          <t>LP055699</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LP055737</t>
+          <t>LP056048</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -767,7 +767,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LP055736</t>
+          <t>LP055700</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LP055442</t>
+          <t>LP056052</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -791,7 +791,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LP055735</t>
+          <t>LP056053</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -803,10 +803,178 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LP055686</t>
+          <t>LP056054</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LP056055</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LP055894</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LP055658</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LP055657</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LP056221</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LP056377</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LP056378</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LP056379</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LP056226</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>LP056380</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>LP056381</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>LP056223</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>LP056220</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Apointing created!</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>LP056219</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>Apointing created!</t>
         </is>

--- a/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
@@ -1,37 +1,168 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\04 - Pointing\01 - LP's\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FD2471-6F1C-480B-AB04-0D15FECBAF2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+  <si>
+    <t>LPs</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>LP-056131</t>
+  </si>
+  <si>
+    <t>LP-055659</t>
+  </si>
+  <si>
+    <t>LP-056136</t>
+  </si>
+  <si>
+    <t>LP-055744</t>
+  </si>
+  <si>
+    <t>LP-056203</t>
+  </si>
+  <si>
+    <t>LP-056994</t>
+  </si>
+  <si>
+    <t>LP-056399</t>
+  </si>
+  <si>
+    <t>LP-056325</t>
+  </si>
+  <si>
+    <t>LP-057929</t>
+  </si>
+  <si>
+    <t>LP-057715</t>
+  </si>
+  <si>
+    <t>LP-057461</t>
+  </si>
+  <si>
+    <t>LP-057462</t>
+  </si>
+  <si>
+    <t>LP-057729</t>
+  </si>
+  <si>
+    <t>LP-057730</t>
+  </si>
+  <si>
+    <t>LP-057864</t>
+  </si>
+  <si>
+    <t>LP-058278</t>
+  </si>
+  <si>
+    <t>LP-057852</t>
+  </si>
+  <si>
+    <t>LP-058204</t>
+  </si>
+  <si>
+    <t>LP-058385</t>
+  </si>
+  <si>
+    <t>LP-058386</t>
+  </si>
+  <si>
+    <t>LP-056408</t>
+  </si>
+  <si>
+    <t>LP-056409</t>
+  </si>
+  <si>
+    <t>LP-056321</t>
+  </si>
+  <si>
+    <t>LP-056552</t>
+  </si>
+  <si>
+    <t>LP-056496</t>
+  </si>
+  <si>
+    <t>LP-056528</t>
+  </si>
+  <si>
+    <t>LP-056529</t>
+  </si>
+  <si>
+    <t>LP-056495</t>
+  </si>
+  <si>
+    <t>LP-056620</t>
+  </si>
+  <si>
+    <t>LP-056621</t>
+  </si>
+  <si>
+    <t>LP-056622</t>
+  </si>
+  <si>
+    <t>LP-056623</t>
+  </si>
+  <si>
+    <t>LP-056836</t>
+  </si>
+  <si>
+    <t>LP-056837</t>
+  </si>
+  <si>
+    <t>LP-056838</t>
+  </si>
+  <si>
+    <t>LP-056839</t>
+  </si>
+  <si>
+    <t>LP-056840</t>
+  </si>
+  <si>
+    <t>Hour</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +177,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,36 +501,320 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>LPs</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>LP056390</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Apointing created!</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38">
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>

--- a/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\04 - Pointing\01 - LP's\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\04 - Pointing\01 - LP's\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB800A6-F398-436E-8490-8F1E886F8BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE330545-4FBE-485F-8398-FCAA0EDEAC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="41">
   <si>
     <t>LPs</t>
   </si>
@@ -103,9 +103,6 @@
     <t>LP-056321</t>
   </si>
   <si>
-    <t>LP-056552</t>
-  </si>
-  <si>
     <t>LP-056496</t>
   </si>
   <si>
@@ -143,6 +140,9 @@
   </si>
   <si>
     <t>LP-056840</t>
+  </si>
+  <si>
+    <t>Error</t>
   </si>
 </sst>
 </file>
@@ -505,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -619,6 +619,9 @@
       <c r="B10">
         <v>12.5</v>
       </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -627,6 +630,9 @@
       <c r="B11">
         <v>20</v>
       </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -635,6 +641,9 @@
       <c r="B12">
         <v>2.5</v>
       </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -643,6 +652,9 @@
       <c r="B13">
         <v>9</v>
       </c>
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -651,6 +663,9 @@
       <c r="B14">
         <v>2.5</v>
       </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -659,6 +674,9 @@
       <c r="B15">
         <v>5</v>
       </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -667,181 +685,239 @@
       <c r="B16">
         <v>12.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
       <c r="B17">
         <v>25</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
       <c r="B18">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
       <c r="B19">
         <v>12.5</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
       <c r="B20">
         <v>16.600000000000001</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
       <c r="B21">
         <v>9</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
       <c r="B22">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
       <c r="B23">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
       <c r="B24">
         <v>8.3000000000000007</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
       <c r="B25">
-        <v>8.3000000000000007</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
       <c r="B26">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
       <c r="B27">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
       <c r="B28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3.3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
       <c r="B29">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>32</v>
       </c>
       <c r="B30">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
       <c r="B31">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
       <c r="B32">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>35</v>
       </c>
       <c r="B33">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
       <c r="B34">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
       <c r="B35">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>38</v>
       </c>
       <c r="B36">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
       <c r="B37">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38">
-        <v>3.3</v>
+      <c r="C37" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\04 - Pointing\01 - LP's\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\04 - Pointing\01 - LP's\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE330545-4FBE-485F-8398-FCAA0EDEAC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AEA20B-3AD0-4C27-B7E8-ADB6F878701C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="39">
   <si>
     <t>LPs</t>
   </si>
@@ -100,9 +100,6 @@
     <t>LP-056409</t>
   </si>
   <si>
-    <t>LP-056321</t>
-  </si>
-  <si>
     <t>LP-056496</t>
   </si>
   <si>
@@ -140,9 +137,6 @@
   </si>
   <si>
     <t>LP-056840</t>
-  </si>
-  <si>
-    <t>Error</t>
   </si>
 </sst>
 </file>
@@ -505,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -771,10 +765,10 @@
         <v>26</v>
       </c>
       <c r="B24">
-        <v>8.3000000000000007</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -782,7 +776,7 @@
         <v>27</v>
       </c>
       <c r="B25">
-        <v>4.0999999999999996</v>
+        <v>3.3</v>
       </c>
       <c r="C25" t="s">
         <v>4</v>
@@ -793,7 +787,7 @@
         <v>28</v>
       </c>
       <c r="B26">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="C26" t="s">
         <v>4</v>
@@ -804,7 +798,7 @@
         <v>29</v>
       </c>
       <c r="B27">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="C27" t="s">
         <v>4</v>
@@ -906,17 +900,6 @@
         <v>3.3</v>
       </c>
       <c r="C36" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37">
-        <v>3.3</v>
-      </c>
-      <c r="C37" t="s">
         <v>4</v>
       </c>
     </row>

--- a/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
+++ b/04 - Pointing/01 - LP's/ApontamentoRodrigo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\04 - Pointing\01 - LP's\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AEA20B-3AD0-4C27-B7E8-ADB6F878701C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F1789D-D519-4096-8B1D-B6F830791D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>LPs</t>
   </si>
@@ -31,112 +31,85 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-056131</t>
-  </si>
-  <si>
-    <t>Apointing created!</t>
-  </si>
-  <si>
-    <t>LP-055659</t>
-  </si>
-  <si>
-    <t>LP-056136</t>
-  </si>
-  <si>
-    <t>LP-055744</t>
-  </si>
-  <si>
-    <t>LP-056203</t>
-  </si>
-  <si>
-    <t>LP-056994</t>
-  </si>
-  <si>
-    <t>LP-056399</t>
-  </si>
-  <si>
-    <t>LP-056325</t>
-  </si>
-  <si>
-    <t>LP-057929</t>
-  </si>
-  <si>
-    <t>LP-057715</t>
-  </si>
-  <si>
-    <t>LP-057461</t>
-  </si>
-  <si>
-    <t>LP-057462</t>
-  </si>
-  <si>
-    <t>LP-057729</t>
-  </si>
-  <si>
-    <t>LP-057730</t>
-  </si>
-  <si>
-    <t>LP-057864</t>
-  </si>
-  <si>
-    <t>LP-058278</t>
-  </si>
-  <si>
-    <t>LP-057852</t>
-  </si>
-  <si>
-    <t>LP-058204</t>
-  </si>
-  <si>
-    <t>LP-058385</t>
-  </si>
-  <si>
-    <t>LP-058386</t>
-  </si>
-  <si>
-    <t>LP-056408</t>
-  </si>
-  <si>
-    <t>LP-056409</t>
-  </si>
-  <si>
-    <t>LP-056496</t>
-  </si>
-  <si>
-    <t>LP-056528</t>
-  </si>
-  <si>
-    <t>LP-056529</t>
-  </si>
-  <si>
-    <t>LP-056495</t>
-  </si>
-  <si>
-    <t>LP-056620</t>
-  </si>
-  <si>
-    <t>LP-056621</t>
-  </si>
-  <si>
-    <t>LP-056622</t>
-  </si>
-  <si>
-    <t>LP-056623</t>
-  </si>
-  <si>
-    <t>LP-056836</t>
-  </si>
-  <si>
-    <t>LP-056837</t>
-  </si>
-  <si>
-    <t>LP-056838</t>
-  </si>
-  <si>
-    <t>LP-056839</t>
-  </si>
-  <si>
-    <t>LP-056840</t>
+    <t>LP-058387</t>
+  </si>
+  <si>
+    <t>LP-058832</t>
+  </si>
+  <si>
+    <t>LP-058232</t>
+  </si>
+  <si>
+    <t>LP-058233</t>
+  </si>
+  <si>
+    <t>LP-058234</t>
+  </si>
+  <si>
+    <t>LP-058235</t>
+  </si>
+  <si>
+    <t>LP-058236</t>
+  </si>
+  <si>
+    <t>LP-057875</t>
+  </si>
+  <si>
+    <t>LP-058237</t>
+  </si>
+  <si>
+    <t>LP-057803</t>
+  </si>
+  <si>
+    <t>LP-058238</t>
+  </si>
+  <si>
+    <t>LP-058247</t>
+  </si>
+  <si>
+    <t>LP-058241</t>
+  </si>
+  <si>
+    <t>LP-058244</t>
+  </si>
+  <si>
+    <t>LP-058245</t>
+  </si>
+  <si>
+    <t>LP-057827</t>
+  </si>
+  <si>
+    <t>LP-058279</t>
+  </si>
+  <si>
+    <t>LP-058280</t>
+  </si>
+  <si>
+    <t>LP-058833</t>
+  </si>
+  <si>
+    <t>LP-058013</t>
+  </si>
+  <si>
+    <t>LP-058097</t>
+  </si>
+  <si>
+    <t>LP-058393</t>
+  </si>
+  <si>
+    <t>LP-058394</t>
+  </si>
+  <si>
+    <t>LP-058395</t>
+  </si>
+  <si>
+    <t>LP-058396</t>
+  </si>
+  <si>
+    <t>LP-058397</t>
+  </si>
+  <si>
+    <t>LP-058398</t>
   </si>
 </sst>
 </file>
@@ -499,12 +472,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -523,384 +496,223 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>2.5</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>2.5</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10">
-        <v>12.5</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11">
-        <v>20</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12">
-        <v>2.5</v>
-      </c>
-      <c r="C12" t="s">
-        <v>4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13">
-        <v>9</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14">
-        <v>2.5</v>
-      </c>
-      <c r="C14" t="s">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15">
-        <v>5</v>
-      </c>
-      <c r="C15" t="s">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>18</v>
       </c>
-      <c r="B16">
-        <v>12.5</v>
-      </c>
-      <c r="C16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B17">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>19</v>
-      </c>
-      <c r="B17">
-        <v>25</v>
-      </c>
-      <c r="C17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>20</v>
       </c>
       <c r="B18">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B19">
-        <v>12.5</v>
-      </c>
-      <c r="C19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B21">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B20">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="C20" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B21">
-        <v>9</v>
-      </c>
-      <c r="C21" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B23">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B22">
-        <v>3.3</v>
-      </c>
-      <c r="C22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B24">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B23">
-        <v>3.3</v>
-      </c>
-      <c r="C23" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B24">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C24" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="B26">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B25">
-        <v>3.3</v>
-      </c>
-      <c r="C25" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B27">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B26">
-        <v>5</v>
-      </c>
-      <c r="C26" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B27">
-        <v>3.3</v>
-      </c>
-      <c r="C27" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28">
-        <v>3.3</v>
-      </c>
-      <c r="C28" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>31</v>
-      </c>
       <c r="B29">
-        <v>3.3</v>
-      </c>
-      <c r="C29" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30">
-        <v>3.3</v>
-      </c>
-      <c r="C30" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31">
-        <v>3.3</v>
-      </c>
-      <c r="C31" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32">
-        <v>3.3</v>
-      </c>
-      <c r="C32" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33">
-        <v>3.3</v>
-      </c>
-      <c r="C33" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34">
-        <v>3.3</v>
-      </c>
-      <c r="C34" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35">
-        <v>3.3</v>
-      </c>
-      <c r="C35" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36">
-        <v>3.3</v>
-      </c>
-      <c r="C36" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
